--- a/apps/admin-web/public/templates/price-card-import-template-PPT-2.xlsx
+++ b/apps/admin-web/public/templates/price-card-import-template-PPT-2.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">本表各行金额的币种，如 CNY</t>
+          <t xml:space="preserve">本表各行金额的币种，取产品内置币种目录里的码，如 CNY</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">期望的类别值；ZONE、ADDRESS_TYPE、SERVICE_OPTION 来源必填，ADDRESS_NATURE 来源必填且只收 COMMERCIAL、RESIDENTIAL</t>
+          <t xml:space="preserve">期望的类别值；类别类来源（ZONE、ADDRESS_TYPE、SERVICE_OPTION、ADDRESS_NATURE）必填。前三者是开放词汇（分区名、偏远档位、服务选项由租户填）；source 为 ADDRESS_NATURE 时只收 COMMERCIAL、RESIDENTIAL</t>
         </is>
       </c>
     </row>
